--- a/event_planner_forms/009_judging_panel_information_form--event_planner_forms.xlsx
+++ b/event_planner_forms/009_judging_panel_information_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'panel_chairperson_1',_'value':_'panel_chair_personnel_1'}</t>
+          <t>panel_chairperson_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Panel Chairperson 1', 'value': 'panel_chair_personnel_1'}</t>
+          <t>Panel Chairperson 1</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'panel_chairperson_2',_'value':_'panel_chair_personnel_2'}</t>
+          <t>panel_chairperson_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Panel Chairperson 2', 'value': 'panel_chair_personnel_2'}</t>
+          <t>Panel Chairperson 2</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'panel_chairperson_3',_'value':_'panel_chair_personnel_3'}</t>
+          <t>panel_chairperson_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Panel Chairperson 3', 'value': 'panel_chair_personnel_3'}</t>
+          <t>Panel Chairperson 3</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'panel_member_1',_'value':_'panel_members_1'}</t>
+          <t>panel_member_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Panel Member 1', 'value': 'panel_members_1'}</t>
+          <t>Panel Member 1</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'panel_member_2',_'value':_'panel_members_2'}</t>
+          <t>panel_member_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Panel Member 2', 'value': 'panel_members_2'}</t>
+          <t>Panel Member 2</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'panel_member_3',_'value':_'panel_members_3'}</t>
+          <t>panel_member_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Panel Member 3', 'value': 'panel_members_3'}</t>
+          <t>Panel Member 3</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'competition',_'value':_'competition'}</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Competition', 'value': 'competition'}</t>
+          <t>Competition</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'audition',_'value':_'audition'}</t>
+          <t>audition</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Audition', 'value': 'audition'}</t>
+          <t>Audition</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'contest',_'value':_'contest'}</t>
+          <t>contest</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Contest', 'value': 'contest'}</t>
+          <t>Contest</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'upcoming',_'value':_'upcoming'}</t>
+          <t>upcoming</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Upcoming', 'value': 'upcoming'}</t>
+          <t>Upcoming</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'past',_'value':_'past'}</t>
+          <t>past</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Past', 'value': 'past'}</t>
+          <t>Past</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress', 'value': 'in_progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
